--- a/fix-invariant/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/fix-invariant/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T12:11:00+00:00</t>
+    <t>2026-07-16T12:36:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -729,7 +729,7 @@
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}FormationCardinality:Formation est obligatoire si typeDroitPrestation = '11.1' (Orientation en Centre de rééducation professionnelle (CRP)). {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='11.1').exists()) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='formation').exists())}PrecisionOrientationValues7.8:Si typeDroitPrestation = '7.8' (Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)) alors precisionOrientation doit être entre '1' et
- '6' {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7.8').exists()) implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code&gt;=1).exists()) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code&lt;=6).exists()))}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation doit être entre '7' et '8' {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7.9').exists()) implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code&gt;=7).exists()) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code&lt;=8).exists()))}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13.1').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13.2').exists())) implies (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists().not())}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation doit être entre '9' et '10'  {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.3').exists()) implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code&gt;=9).exists()) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code&lt;=10).exists()))}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.6').exists()) implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='UEA').exists()) or (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='UEM').exists()))}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Adultes) ou '7' (Orientation ESMS Enfants) alors temporaliteAccueil est obligatoire. {((extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13').exists()) or (extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7')).exists()) implies (extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.6').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.7').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.8').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.10').exists())) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='creton').exists())}</t>
+ '6' {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7.8').exists()) implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code.toInteger()&gt;=1).exists()) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code.toInteger()&lt;=6).exists()))}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation doit être entre '7' et '8' {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7.9').exists()) implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code.toInteger()&gt;=7).exists()) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code.toInteger()&lt;=8).exists()))}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13.1').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13.2').exists())) implies (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists().not())}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation doit être entre '9' et '10'  {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.3').exists()) implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code.toInteger()&gt;=9).exists()) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code.toInteger()&lt;=10).exists()))}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.6').exists()) implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='UEA').exists()) or (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='UEM').exists()))}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Adultes) ou '7' (Orientation ESMS Enfants) alors temporaliteAccueil est obligatoire. {((extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13').exists()) or (extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7')).exists()) implies (extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.6').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.7').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.8').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.10').exists())) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='creton').exists())}</t>
   </si>
   <si>
     <t>DroitPrestation</t>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>78</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>87</v>

--- a/fix-invariant/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/fix-invariant/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T12:36:44+00:00</t>
+    <t>2026-07-16T13:49:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -729,7 +729,16 @@
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}FormationCardinality:Formation est obligatoire si typeDroitPrestation = '11.1' (Orientation en Centre de rééducation professionnelle (CRP)). {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='11.1').exists()) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='formation').exists())}PrecisionOrientationValues7.8:Si typeDroitPrestation = '7.8' (Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)) alors precisionOrientation doit être entre '1' et
- '6' {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7.8').exists()) implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code.toInteger()&gt;=1).exists()) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code.toInteger()&lt;=6).exists()))}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation doit être entre '7' et '8' {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7.9').exists()) implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code.toInteger()&gt;=7).exists()) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code.toInteger()&lt;=8).exists()))}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13.1').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13.2').exists())) implies (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists().not())}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation doit être entre '9' et '10'  {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.3').exists()) implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code.toInteger()&gt;=9).exists()) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code.toInteger()&lt;=10).exists()))}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.6').exists()) implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='UEA').exists()) or (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='UEM').exists()))}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Adultes) ou '7' (Orientation ESMS Enfants) alors temporaliteAccueil est obligatoire. {((extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13').exists()) or (extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7')).exists()) implies (extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.6').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.7').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.8').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.10').exists())) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='creton').exists())}</t>
+ '6' {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7.8').exists())
+implies
+(  extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(
+    code='1' or code='2' or code='3' or code='4' or code='5' or code='6'
+  ).exists()
+)}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation doit être entre '7' et '8' {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7.9').exists())
+ implies
+ (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='7' or code='8').exists())}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13.1').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13.2').exists())) implies (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists().not())}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation doit être entre '9' et '10'  {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.3').exists())
+ implies
+  (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='9' or code='10').exists())}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.6').exists()) implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='UEA').exists()) or (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='UEM').exists()))}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Adultes) ou '7' (Orientation ESMS Enfants) alors temporaliteAccueil est obligatoire. {((extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13').exists()) or (extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7')).exists()) implies (extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.6').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.7').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.8').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.10').exists())) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='creton').exists())}</t>
   </si>
   <si>
     <t>DroitPrestation</t>

--- a/fix-invariant/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/fix-invariant/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T13:49:33+00:00</t>
+    <t>2026-07-16T14:55:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -729,16 +729,39 @@
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}FormationCardinality:Formation est obligatoire si typeDroitPrestation = '11.1' (Orientation en Centre de rééducation professionnelle (CRP)). {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='11.1').exists()) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='formation').exists())}PrecisionOrientationValues7.8:Si typeDroitPrestation = '7.8' (Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)) alors precisionOrientation doit être entre '1' et
- '6' {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7.8').exists())
+ '6' {(
+  extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7.8').exists()
+  and
+  extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists()
+)
 implies
-(  extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(
-    code='1' or code='2' or code='3' or code='4' or code='5' or code='6'
-  ).exists()
-)}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation doit être entre '7' et '8' {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7.9').exists())
- implies
- (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='7' or code='8').exists())}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13.1').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13.2').exists())) implies (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists().not())}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation doit être entre '9' et '10'  {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.3').exists())
- implies
-  (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='9' or code='10').exists())}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.6').exists()) implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='UEA').exists()) or (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='UEM').exists()))}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Adultes) ou '7' (Orientation ESMS Enfants) alors temporaliteAccueil est obligatoire. {((extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13').exists()) or (extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7')).exists()) implies (extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.6').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.7').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.8').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.10').exists())) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='creton').exists())}</t>
+(
+  extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='1' or code='2' or code='3' or code='4' or code='5' or code='6').exists()
+)}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation doit être entre '7' et '8' {(
+  extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7.9').exists()
+  and
+  extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists()
+)
+implies
+(
+  extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='7' or code='8').exists()
+)}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13.1').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13.2').exists())) implies (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists().not())}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation doit être entre '9' et '10'  {(
+  extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.3').exists()
+  and
+  extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists()
+)
+implies
+(
+  extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='9' or code='10').exists()
+)}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(
+  extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.6').exists()
+  and
+  extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists()
+)
+implies
+(
+  extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.where(code='UEA' or code='UEM').exists()
+)}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Adultes) ou '7' (Orientation ESMS Enfants) alors temporaliteAccueil est obligatoire. {((extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='13').exists()) or (extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7')).exists()) implies (extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.6').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.7').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.8').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.where(code='8.10').exists())) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.where(code='7').exists()) or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='creton').exists())}</t>
   </si>
   <si>
     <t>DroitPrestation</t>

--- a/fix-invariant/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/fix-invariant/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.4.0-ballot</t>
+    <t>2.4.0-tru</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:57:40+00:00</t>
+    <t>2026-07-23T07:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -857,7 +857,7 @@
     <t>Basic.extension:TDDUIDecision.extension:droitPrestation.extension:natureDroitPrestation.value[x]</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j400-nature-droit-prestation-ms</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/jdv-j400-nature-droit-prestation-ms-tru</t>
   </si>
   <si>
     <t>Basic.extension:TDDUIDecision.extension:droitPrestation.extension:dateOuverture</t>
